--- a/assets/constructions/examples/ctd_bs_arbor.xlsx
+++ b/assets/constructions/examples/ctd_bs_arbor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HSK100A-DCK4-100</t>
+          <t>BT50-FMS40-300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,9 +614,11 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -604,32 +626,32 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>DER_DCK:4</t>
+          <t>DER_FMS</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>DER_DCK:4</t>
+          <t>DER_FMS</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -641,7 +663,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>2.8</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -650,12 +672,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>27698.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK40-DCK1-70</t>
+          <t>HSK100A-FMX40-150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -666,9 +702,11 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="F3" t="n">
+        <v>160</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -676,32 +714,32 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>DIN_69871:SK40</t>
+          <t>ISO_12164_1_2013:HSK100A</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>DER_DCK:1</t>
+          <t>DER_FMX</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>DER_DCK:1</t>
+          <t>DER_FMX</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -713,7 +751,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>10.53</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -722,84 +760,116 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>651.2</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>53381.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HSK63A-DCK3-100</t>
+          <t>BT 30 MB32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ISCAR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BT-MB</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>10.6</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>100</v>
-      </c>
+      <c r="L4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK63A</t>
+          <t>JIS_B_6339_MAS_403:BT30</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DAN_MB32</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DAN_MB32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>DANDREA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>1.1</v>
+        <v>0.38</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
-        </is>
-      </c>
+          <t>2020 / www.iscar.com</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK50-DCK3-140L</t>
+          <t>BT50-NBH-B100</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -810,7 +880,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -820,32 +890,32 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>DIN_69871:SK50</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER_NBH</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER_NBH</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -857,7 +927,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>4.09</v>
+        <v>4.84</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -866,12 +936,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>235.98</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>19344.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT40-DCK5-100</t>
+          <t>BBT40-DCK4-43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -882,7 +966,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -892,7 +976,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -907,17 +991,17 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT40</t>
+          <t>JIS_B_6339_MAS_403:BBT40</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DER_DCK:5</t>
+          <t>DER_DCK:4</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>DER_DCK:5</t>
+          <t>DER_DCK:4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -929,7 +1013,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -939,6 +1023,12 @@
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
       </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
